--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R590d369223504e40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Ra4479cc3498c4be5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="Rbb378f87db8c41f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="R144d727c1aa84af1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3405,6 +3405,28 @@
         <x:v>EGO와 EGO 기프트 결과 화면에서 정답 정보와 이미지가 추측 기록보다 먼저 보이도록 상단으로 옮겼습니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="131" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A131" t="str">
+        <x:v>v0.16.0</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>2026-09-17</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>EGO와 EGO 기프트 퀴즈에 필요한 정보만 고르는 선택형 힌트 패널 추가.
+추측 1회와 유료 힌트 1개를 각각 비용 1로 합산하고, 정답 시 비용 1~2 ALEPH·3~4 WAW·5~6 HE·7~8 TETH·9 이상 ZAYIN 관리자 평가 적용.
+EGO와 EGO 기프트의 힌트·비용 상태를 독립 저장해 일일 진행 복원과 결과·공유 카드에 반영.
+EGO 기프트는 첫 효과 기록을 무료로 제공하고 이후 효과 기록을 수동 공개하도록 변경. 등급·조건 속성·이름 길이·강화 가능·키워드도 개별 공개 가능.
+전용 테마 팩 정보를 효과 기록 단서에 포함하고 기프트 데이터 441개 재빌드.
+브라우저에서 선택 힌트 비용, 오답 추측 비용, 효과 기록 수동 공개, 키워드 가림 해제와 콘솔 오류 없음 확인.</x:v>
+      </x:c>
+      <x:c r="D131" t="str">
+        <x:v>EGO와 EGO 기프트 퀴즈에 원하는 힌트만 골라 보는 기능을 추가했습니다. 추측과 유료 힌트는 각각 비용 1이며, 비용이 적을수록 ALEPH에 가까운 높은 관리자 평가를 받습니다.
+EGO와 기프트의 비용은 서로 섞이지 않습니다. 기프트의 첫 효과 기록은 무료이며, 다음 효과 기록과 등급·조건 속성·이름 길이·강화 가능·키워드를 필요한 만큼 직접 열 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="E131"/>
+      <x:c r="F131"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="Rbb378f87db8c41f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="R144d727c1aa84af1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="Rcf7c83718efb4565"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Rfb57ed8535ad44ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3427,6 +3427,39 @@
       <x:c r="E131"/>
       <x:c r="F131"/>
     </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>v0.16.1</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>2026-09-17</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>홈 화면에 최신 반영 인격 상태 표시를 추가함. identityUpdates.json의 마지막 identity 항목을 data.json과 연결해 인격명과 ID를 표시하고, 전체 인격 수도 함께 갱신함. 비동기 로드 순서와 업데이트 목록 누락 시 폴백 문구를 처리함.</x:v>
+      </x:c>
+      <x:c r="D132" t="str">
+        <x:v>홈 화면에서 사이트에 마지막으로 반영된 인격의 이름과 ID, 전체 인격 수를 확인할 수 있습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="57.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A133" t="str">
+        <x:v>v0.16.2</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>2026-09-17</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>EGO 자원 구성 힌트를 클릭마다 자원 1개씩 공개하도록 변경하고, 각 자원 공개를 힌트 비용 1로 독립 합산함. 일일 상태와 결과 기록에 resourceRevealCount를 저장하며 구버전 저장 상태도 호환 처리함.
+공개된 힌트 버튼의 disabled opacity를 해제하고 대비·배경·테두리를 강화해 열린 정보를 선명하게 표시함.
+EGO 기프트 효과 기록의 기본 무료 공개를 제거하고 0개 공개 상태에서 시작하도록 변경함. 첫 효과 기록부터 공개할 때마다 비용 1을 부과함.
+검증: EGO 자원 0/5→1/5 비용 1→2/5 비용 2, 기프트 효과 0/2→1/2 비용 1, ALEPH/WAW 예상 등급 전환과 브라우저 콘솔 오류 없음을 확인함.</x:v>
+      </x:c>
+      <x:c r="D133" t="str">
+        <x:v>EGO 자원 구성은 누를 때마다 자원 하나씩 공개되며, 각각 힌트 비용 1로 계산됩니다.
+열어 본 힌트는 흐려지지 않고 선명하게 표시됩니다.
+EGO 기프트 효과 기록은 처음부터 보이지 않으며 첫 기록부터 비용 1을 내고 열어야 합니다. 따라서 ALEPH는 힌트를 최대 1개만 열고 첫 추측에 맞힌 경우까지 받을 수 있습니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="Rcf7c83718efb4565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Rfb57ed8535ad44ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R454e4b8b5d5a4472"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Rb02321093241439e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3460,6 +3460,20 @@
 EGO 기프트 효과 기록은 처음부터 보이지 않으며 첫 기록부터 비용 1을 내고 열어야 합니다. 따라서 ALEPH는 힌트를 최대 1개만 열고 첫 추측에 맞힌 경우까지 받을 수 있습니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>v0.16.3</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>2026-09-17</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>기존 EGOData의 '입주 신고' 히스클리프(ID 119) 행을 유지하고 아이콘 경로를 신규 원본 PNG(./images/ego/119.png)로 교체함. build-content-updates.js에 latestIdentityId를 별도 보존해 신규 EGO만 감지된 빌드에서도 홈의 최신 인격 표시가 유지되도록 수정. 신규 콘텐츠 안내는 EGO 119만 최초 1회 표시되도록 검증.</x:v>
+      </x:c>
+      <x:c r="D134" t="str">
+        <x:v>히스클리프 EGO '입주 신고'의 원본 이미지를 추가했습니다. 새로 접속하면 신규 EGO 안내에서 한 번 확인할 수 있습니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R454e4b8b5d5a4472"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Rb02321093241439e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R3700b3330e5a4c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Re3a6d97caf8c44b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3474,6 +3474,20 @@
         <x:v>히스클리프 EGO '입주 신고'의 원본 이미지를 추가했습니다. 새로 접속하면 신규 EGO 안내에서 한 번 확인할 수 있습니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>v0.16.4</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>2026-09-17</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>홈의 최신 반영 상태를 인격과 EGO 두 행으로 확장함. identityUpdates.json에 latestEgoId를 별도 저장하고, 신규 인격 또는 EGO만 추가된 빌드에서도 두 최신 항목을 각각 유지하도록 build-content-updates.js를 수정함. EGO 데이터 로드 완료 시 이름, 수감자, 등급, ID, 전체 EGO 수를 갱신하도록 처리함.</x:v>
+      </x:c>
+      <x:c r="D135" t="str">
+        <x:v>홈 화면에서 마지막으로 반영된 인격과 EGO를 함께 확인할 수 있습니다. EGO만 업데이트된 경우에도 최신 EGO 이름, 수감자, 등급, ID가 표시됩니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R3700b3330e5a4c84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Re3a6d97caf8c44b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R9a9b76d4488c4664"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="R4d9565e1cbcc44c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3488,6 +3488,37 @@
         <x:v>홈 화면에서 마지막으로 반영된 인격과 EGO를 함께 확인할 수 있습니다. EGO만 업데이트된 경우에도 최신 EGO 이름, 수감자, 등급, ID가 표시됩니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>v0.16.5</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>홈 최신 반영 상태에서 내부 ID 문구를 제거함. 인격·EGO 행을 각각 키보드 접근 가능한 버튼으로 바꾸고, 선택한 종류의 최신 추가 카드만 신규 콘텐츠 팝업에 표시하도록 연결함.</x:v>
+      </x:c>
+      <x:c r="D136" t="str">
+        <x:v>홈의 최신 반영 인격과 EGO에서 ID 표기를 제거했습니다.
+최신 인격과 최신 EGO를 각각 누르면 해당 종류의 추가 소식을 따로 확인할 수 있습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>v0.16.6</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>신규 인격 오트쿠튀르::수선실 로쟈(ID 10917)와 신규 EGO 거울촉각 로쟈(ID 128), 거절선포 홍루(ID 129)의 데이터·WebP 이미지를 추가함. identityUpdates.json에 latestIdentityIds/latestEgoIds 배열을 도입해 동일 빌드에서 같은 종류가 여러 개 추가돼도 홈 상태와 종류별 팝업이 전부 표시하도록 확장하고 기존 단일 ID 필드 폴백을 유지함.</x:v>
+      </x:c>
+      <x:c r="D137" t="str">
+        <x:v>신규 인격 '오트쿠튀르::수선실 로쟈'를 추가했습니다.
+신규 EGO '거울촉각 로쟈'와 '거절선포 홍루'를 추가했습니다.
+같은 업데이트에 인격이나 EGO가 여러 개 추가되면 홈 최신 반영 상태와 팝업에 모두 표시됩니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3654,6 +3654,33 @@
 TRY 기록의 항목별 일치 판정과 방향 표시를 없애고, 제출한 EGO·기프트의 큰 이미지와 정보를 표시합니다. EGO 이미지는 원형으로 통일했으며 정답 TRY는 초록색으로 강조합니다.
 상단에 도움말과 포기 버튼을 모으고 안내 문구를 정리했습니다. 결과에는 전체 등급 기준과 내 등급이 표시됩니다.
 죄악 아이콘을 개선하고, 빌드 후 index.html 파일을 직접 열어도 퀴즈 데이터를 불러올 수 있도록 수정했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>v0.16.8</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>이미지 퀴즈 데이터·빌드·검증 스크립트 및 로컬 WebP 자산 추가.
+일일 엔케팔린 기록·등급 산정·과거 기록 재계산·활동 그래프·지령 카드 회수 미터 구현.
+ZAYIN/TETH/HE/WAW/ALEPH 등급 WebP 자산과 EGO·기프트 결과 평가 표식 통합.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>관리자 식별 교육에 인물·보스·패닉 이미지 퀴즈를 추가했습니다.
+오늘의 인격·EGO·EGO 기프트에 엔케팔린 배정량과 회수량을 적용하고, 획득량에 따라 ZAYIN부터 ALEPH까지 등급을 표시합니다.
+홈에 최근 7일 엔케팔린 획득량과 일별 종합 등급을 보여주는 액체 막대 그래프를 추가했습니다.
+오늘의 지령 카드에서 등급 이미지, 획득 엔케팔린, 배정량 대비 회수 바를 함께 확인할 수 있습니다.</t>
         </is>
       </c>
     </row>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R3b3ed0bc462a45e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Ra916c258ab7d442f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="Rd9d5960b308f4866"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Rb97344e3db2f4674"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3695,6 +3695,20 @@
 TRY 번호는 실제 제출 순서대로 유지됩니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>v0.16.10</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>오늘의 EGO와 EGO 기프트 결과 화면에서 정답 이미지를 관리자 등급 영역 바로 아래로 이동. 엔케팔린 회수 결과와 전체 등급 기준표를 하나의 통합 카드로 묶고, 상세 정보와 효과는 이미지 아래에 배치. 두 결과 렌더러의 순서를 검증하는 회귀 테스트 추가.</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
+        <x:v>오늘의 EGO와 EGO 기프트 결과에서 엔케팔린 회수 등급과 등급 기준표가 하나의 카드로 표시됩니다. 그 아래에 정답 이미지가 크게 나오고, 상세 정보와 효과가 이어집니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="Rd9d5960b308f4866"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="Rb97344e3db2f4674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog" sheetId="1" r:id="R2e7fe00b7ad14933"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UpdateLog_백업" sheetId="2" r:id="R9aaf53c467b2413a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,6 +14,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="1">
     <x:font>
       <x:sz val="12"/>
@@ -35,8 +38,9 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -3709,6 +3713,38 @@
         <x:v>오늘의 EGO와 EGO 기프트 결과에서 엔케팔린 회수 등급과 등급 기준표가 하나의 카드로 표시됩니다. 그 아래에 정답 이미지가 크게 나오고, 상세 정보와 효과가 이어집니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="142" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A142" t="str">
+        <x:v>v0.16.11</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>2026-10-02</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>인격 두들의 소속 판정을 키워드와 같은 3단계 규칙으로 통합함. 같은 소속 열은 일치(초록), 정답의 다른 소속 열에 존재하면 순서 다름(노랑), 정답에 없으면 불일치(빨강)로 처리하며, LCD 현장추리팀 이스마엘의 검계 소속처럼 소속1과 소속3이 교차하는 사례를 포함한 회귀 테스트와 판정 명세를 추가함.</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
+        <x:v>인격 두들의 소속 판정을 수정했습니다.
+같은 소속이 정답의 다른 칸에 있으면 이제 빨강이 아니라 노랑(순서 다름)으로 표시됩니다.
+LCD 현장추리팀 이스마엘의 검계 소속도 올바르게 판정됩니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A143" t="str">
+        <x:v>v0.16.12</x:v>
+      </x:c>
+      <x:c r="B143" s="1" t="str">
+        <x:v>2026-10-06</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>신규 인격 오트쿠튀르::르누아르 브랜드 매니저 돈키호테(ID 10315)의 데이터와 일반·각성·공격 스킬 3종 WebP 이미지를 추가하고 방어 스킬 묵시 이미지를 별도 보관함. 신규 EGO 구멍 파우스트(ID 130)와 구멍 뫼르소(ID 131)의 데이터·WebP 이미지를 추가함. 홈 최신 반영 상태와 종류별 신규 콘텐츠 팝업에 이번 추가 항목이 표시되도록 갱신함.</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
+        <x:v>신규 인격 '오트쿠튀르::르누아르 브랜드 매니저 돈키호테'와 스킬 이미지를 추가했습니다.
+신규 EGO '구멍 파우스트'와 '구멍 뫼르소'를 추가했습니다.
+홈의 최신 반영 상태와 신규 콘텐츠 팝업에서도 확인할 수 있습니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -66,9 +66,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -121,14 +120,74 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -180,7 +239,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -189,13 +248,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -229,6 +288,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -283,12 +353,53 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D145"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -330,6 +441,9 @@
       <c r="C3" t="str">
         <v>초기 안정화</v>
       </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
@@ -488,6 +602,9 @@
       <c r="C14" t="str">
         <v>버전 표시 갱신</v>
       </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15" xml:space="preserve">
       <c r="A15" t="str">
@@ -560,6 +677,9 @@
       <c r="C19" t="str">
         <v>정답 이미지 로드 완료 후 재스크롤하여 화면 중앙 정렬 보정</v>
       </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -628,6 +748,9 @@
       </c>
       <c r="C24" t="str">
         <v>CharacterTable.xlsx 스킬1/2/3 정보(명칭·속성·유형·아이콘) 최신화 반영</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -865,6 +988,9 @@
       <c r="C39" t="str">
         <v>덱 빌더: 후보 목록에서 "없음" 카드가 각 수감자 탭에서 항상 맨 앞에 오도록 정렬</v>
       </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -911,6 +1037,9 @@
 수감자-인격명이 뒤바뀐 오류 1건, 이름 오탈자 2건, 이름 누락 2건 등 실제 데이터 불일치 수정_x000d__x000d_
 Type 칸의 대소문자 표기 불일치(sub → Sub) 5건 수정 (판정 로직에서 정답으로 인식되지 않던 버그)</v>
       </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -939,6 +1068,9 @@
 Main 순서 판정을 절대 슬롯 위치가 아닌 배치된 Main 카드들끼리의 상대 순서로 비교하도록 개선_x000d__x000d_
 (참고: "중지덱"의 순서값이 1,2,3,7로 비연속인 데이터 이슈 발견, DeckData 시트 확인 필요)</v>
       </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45" t="str">
@@ -1015,6 +1147,9 @@
 좁은 좌측 패널에서 헤더 버튼이 줄바꿈되던 문제 수정_x000d__x000d_
 제출 버튼을 헤더 바로 아래로 이동, 슬롯 영역 내부 스크롤 제거</v>
       </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50" xml:space="preserve">
       <c r="A50" t="str">
@@ -1028,6 +1163,9 @@
 좁은 좌측 패널 안에 있던 버튼들을 분리해 좌우 분할 시에도 넉넉하게 표시_x000d__x000d_
 모바일에서 타이틀 텍스트가 세로로 깨지던 문제 수정</v>
       </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51" xml:space="preserve">
       <c r="A51" t="str">
@@ -1041,6 +1179,9 @@
 상단 제출 버튼을 매우 크게 강조 표시로 변경_x000d__x000d_
 좌우 패널 비율을 300px 고정에서 50:50으로 변경, 카드/슬롯 확대</v>
       </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52" xml:space="preserve">
       <c r="A52" t="str">
@@ -1052,6 +1193,9 @@
       <c r="C52" t="str" xml:space="preserve">
         <v xml:space="preserve">덱 빌더: 아무 수감자의 없음 카드나 넣어도 정답 처리되던 채점 버그 수정_x000d__x000d_
 없음 카드는 해당 슬롯이 요구하는 수감자와 일치할 때만 정답으로 인정</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53" xml:space="preserve">
@@ -1065,6 +1209,9 @@
         <v xml:space="preserve">Main 카드 하나만 배치해도 정답으로 잠기던 채점/잠금 버그 수정_x000d__x000d_
 Main 슬롯은 덱이 요구하는 Main 전원이 동시에 정답일 때만 잠기도록 변경_x000d__x000d_
 다른 Main 배치가 바뀌면 이전에 맞았던 자리가 다시 틀릴 수 있어 섣불리 잠그지 않게 함</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54" xml:space="preserve">
@@ -1095,6 +1242,9 @@
 Sub 인격은 위치 무관, 없음 카드는 뒤쪽 슬롯으로 자동 정렬_x000d__x000d_
 제출 시 정답으로 확인된 카드를 올바른 자리로 자동 재배치 후 고정(영구 잠김 충돌 방지)</v>
       </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56" xml:space="preserve">
       <c r="A56" t="str">
@@ -1139,6 +1289,9 @@
 Sub나 없음이 어떤 Main의 정답 순서 칸(order 자리)에 있으면 노랑(순서 다름) 처리_x000d__x000d_
 해당 자리를 비워줘야 그 Main이 정상적으로 정답 처리될 수 있음</v>
       </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59" xml:space="preserve">
       <c r="A59" t="str">
@@ -1151,6 +1304,9 @@
         <v xml:space="preserve">인격 이미지(일반/각성) 및 스킬 아이콘을 로컬 파일로 교체_x000d__x000d_
 외부 CDN 대신 프로젝트 내 이미지를 사용해 로딩 안정성 향상</v>
       </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60" xml:space="preserve">
       <c r="A60" t="str">
@@ -1162,6 +1318,9 @@
       <c r="C60" t="str" xml:space="preserve">
         <v xml:space="preserve">CharacterTable에 ID열(A열) 추가_x000d__x000d_
 인격 고유 번호를 데이터에 노출해 추후 참조/매칭에 사용할 수 있도록 함</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61" xml:space="preserve">
@@ -1191,6 +1350,9 @@
 DeckData의 Deck 컬럼이 삭제되면서 배포판 덱 이름이 빈 값으로 나오던 버그 수정_x000d__x000d_
 덱 키워드(deckKeywords.json) 빌드 결과물 신규 추가(향후 힌트 기능용)</v>
       </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63" xml:space="preserve">
       <c r="A63" t="str">
@@ -1202,6 +1364,9 @@
       <c r="C63" t="str" xml:space="preserve">
         <v xml:space="preserve">덱 빌더: 왼쪽 슬롯 패널의 고정(sticky) 스크롤 제거_x000d__x000d_
 페이지 전체가 하나로 자연스럽게 스크롤되도록 변경</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64" xml:space="preserve">
@@ -1247,6 +1412,9 @@
         <v xml:space="preserve">오늘의 인격/랜덤 플레이: 공유하기 버튼을 정답 카드 안으로 이동_x000d__x000d_
 정답 공개 시 자동 스크롤 후에도 공유 버튼이 바로 보이도록 개선_x000d__x000d_
 일치/불일치/취소선 테스트 설명을 하단 추측 기록 카드로 이동</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
       </c>
     </row>
     <row r="67" xml:space="preserve">
@@ -1324,6 +1492,9 @@
 changelog.json은 사용자용 Log가 채워진 행만 포함하도록 빌드 스크립트 수정_x000d__x000d_
 전체 버전이 담긴 changelog_dev.json은 dev/ 폴더에 생성하고 .vercelignore로 배포 제외</v>
       </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72" xml:space="preserve">
       <c r="A72" t="str">
@@ -1335,6 +1506,9 @@
       <c r="C72" t="str" xml:space="preserve">
         <v xml:space="preserve">.vercelignore는 빌드 중 새로 생성되는 파일에는 적용되지 않아 changelog_dev.json이 실제로는 공개 배포되고 있던 것을 발견하고 수정_x000d__x000d_
 Vercel 빌드 환경(VERCEL=1)에서는 changelog_dev.json 자체를 생성하지 않도록 변경, 로컬에서는 그대로 생성됨</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
       </c>
     </row>
     <row r="73" xml:space="preserve">
@@ -2421,7 +2595,7 @@
         <v>EGO와 EGO 기프트 결과 화면에서 정답 정보와 이미지가 추측 기록보다 먼저 보이도록 상단으로 옮겼습니다.</v>
       </c>
     </row>
-    <row r="131" ht="86.4000015258789" customHeight="1" xml:space="preserve">
+    <row r="131" xml:space="preserve">
       <c r="A131" t="str">
         <v>v0.16.0</v>
       </c>
@@ -2455,7 +2629,7 @@
         <v>홈 화면에서 사이트에 마지막으로 반영된 인격의 이름과 ID, 전체 인격 수를 확인할 수 있습니다.</v>
       </c>
     </row>
-    <row r="133" ht="57.599998474121094" customHeight="1" xml:space="preserve">
+    <row r="133" xml:space="preserve">
       <c r="A133" t="str">
         <v>v0.16.2</v>
       </c>
@@ -2605,7 +2779,7 @@
         <v>오늘의 EGO와 EGO 기프트 결과에서 엔케팔린 회수 등급과 등급 기준표가 하나의 카드로 표시됩니다. 그 아래에 정답 이미지가 크게 나오고, 상세 정보와 효과가 이어집니다.</v>
       </c>
     </row>
-    <row r="142" ht="43.20000076293945" customHeight="1" xml:space="preserve">
+    <row r="142" xml:space="preserve">
       <c r="A142" t="str">
         <v>v0.16.11</v>
       </c>
@@ -2621,11 +2795,11 @@
 LCD 현장추리팀 이스마엘의 검계 소속도 올바르게 판정됩니다.</v>
       </c>
     </row>
-    <row r="143" ht="43.20000076293945" customHeight="1" xml:space="preserve">
+    <row r="143" xml:space="preserve">
       <c r="A143" t="str">
         <v>v0.16.12</v>
       </c>
-      <c r="B143" s="1" t="str">
+      <c r="B143" t="str">
         <v>2026-10-06</v>
       </c>
       <c r="C143" t="str">
@@ -2652,10 +2826,25 @@
 홈의 최신 반영 상태와 신규 콘텐츠 팝업에서도 확인할 수 있습니다.</v>
       </c>
     </row>
+    <row r="145" xml:space="preserve">
+      <c r="A145" t="str">
+        <v>v0.17.0</v>
+      </c>
+      <c r="B145" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="C145" t="str">
+        <v>오늘의 EGO에서 수감자·등급·속성 세 힌트만으로 115개 중 105개가 유일하게 특정되는 문제를 해결함. 수감자 힌트는 추측 2회 제출 후에만 열리도록 잠그고(EQ_SINNER_HINT_UNLOCK_TRIES), 각성 스킬 효과를 줄 단위로 최대 6단계 공개하는 유료 힌트를 추가함. 효과문에서 EGO 이름은 항상, 수감자·속성은 해당 힌트를 열기 전까지 가림. scripts/fetch-ego-effects.js를 추가해 limbusdeck.com 상세 페이지에서 각성 스킬 효과문을 긁어 EGOData 시트의 효과 열만 채우고, build-egos.js가 효과 필드를 egoData.json에 포함하도록 함. 일일 저장 상태와 기록에 effectRevealCount를 포함해 복원함.</v>
+      </c>
+      <c r="D145" t="str" xml:space="preserve">
+        <v xml:space="preserve">오늘의 EGO에 각성 스킬 효과 힌트가 추가됐습니다. 한 줄씩 공개되며 줄마다 엔케팔린 1을 소모합니다.
+효과문에서 EGO 이름은 가려지고, 수감자와 속성은 해당 힌트를 열어야 드러납니다.
+수감자 힌트는 추측을 2회 제출한 뒤부터 열 수 있습니다.</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D144"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D145"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/UpdateLog.xlsx
+++ b/UpdateLog.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D146"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2842,9 +2842,24 @@
 수감자 힌트는 추측을 2회 제출한 뒤부터 열 수 있습니다.</v>
       </c>
     </row>
+    <row r="146" xml:space="preserve">
+      <c r="A146" t="str">
+        <v>v0.17.1</v>
+      </c>
+      <c r="B146" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="C146" t="str">
+        <v>오늘의 EGO에 키워드 힌트를 추가함. limbusdeck.com 각성 스킬 카드의 키워드 배지(예: 출혈 (부여), 호흡 (강화))를 fetch-ego-effects.js가 함께 수집해 EGOData 시트의 키워드 열에 저장하고, build-egos.js가 egoData.json에 포함함. 힌트 패널과 결과 화면에서 kwChip 색상으로 표시하며, 배지가 없는 EGO 35개는 없음으로 표시함.</v>
+      </c>
+      <c r="D146" t="str" xml:space="preserve">
+        <v xml:space="preserve">오늘의 EGO에 키워드 힌트가 추가됐습니다. 각성 스킬이 부여·강화·소모하는 키워드를 보여줍니다.
+키워드가 없는 EGO는 없음으로 표시됩니다.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D146"/>
   </ignoredErrors>
 </worksheet>
 </file>
